--- a/backend_HRMS/website/templates/Expenses_Claim_Form_FT.xlsx
+++ b/backend_HRMS/website/templates/Expenses_Claim_Form_FT.xlsx
@@ -797,7 +797,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1206,6 +1206,47 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1844,10 +1885,10 @@
       <c r="G14" s="150" t="n"/>
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="17" t="n"/>
-      <c r="J14" s="75" t="n"/>
-      <c r="K14" s="75" t="n"/>
-      <c r="L14" s="74" t="n"/>
-      <c r="M14" s="45" t="n"/>
+      <c r="J14" s="160" t="n"/>
+      <c r="K14" s="160" t="n"/>
+      <c r="L14" s="161" t="n"/>
+      <c r="M14" s="162" t="n"/>
       <c r="P14" s="62" t="inlineStr">
         <is>
           <t>Advance Payment</t>
@@ -1873,10 +1914,10 @@
       <c r="G15" s="135" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="77" t="n"/>
-      <c r="J15" s="72" t="n"/>
-      <c r="K15" s="72" t="n"/>
-      <c r="L15" s="71" t="n"/>
-      <c r="M15" s="46" t="n"/>
+      <c r="J15" s="163" t="n"/>
+      <c r="K15" s="163" t="n"/>
+      <c r="L15" s="164" t="n"/>
+      <c r="M15" s="165" t="n"/>
       <c r="P15" s="35" t="inlineStr">
         <is>
           <t>Date</t>
@@ -1922,10 +1963,10 @@
       <c r="G16" s="135" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="77" t="n"/>
-      <c r="J16" s="72" t="n"/>
-      <c r="K16" s="72" t="n"/>
-      <c r="L16" s="71" t="n"/>
-      <c r="M16" s="46" t="n"/>
+      <c r="J16" s="163" t="n"/>
+      <c r="K16" s="163" t="n"/>
+      <c r="L16" s="164" t="n"/>
+      <c r="M16" s="165" t="n"/>
       <c r="P16" s="36" t="n"/>
       <c r="Q16" s="34" t="n"/>
       <c r="R16" s="34" t="n"/>
@@ -1945,10 +1986,10 @@
       <c r="G17" s="135" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="77" t="n"/>
-      <c r="J17" s="72" t="n"/>
-      <c r="K17" s="72" t="n"/>
-      <c r="L17" s="72" t="n"/>
-      <c r="M17" s="46" t="n"/>
+      <c r="J17" s="163" t="n"/>
+      <c r="K17" s="163" t="n"/>
+      <c r="L17" s="163" t="n"/>
+      <c r="M17" s="165" t="n"/>
       <c r="P17" s="36" t="n"/>
       <c r="Q17" s="34" t="n"/>
       <c r="R17" s="34" t="n"/>
@@ -1968,10 +2009,10 @@
       <c r="G18" s="135" t="n"/>
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="77" t="n"/>
-      <c r="J18" s="72" t="n"/>
-      <c r="K18" s="72" t="n"/>
-      <c r="L18" s="72" t="n"/>
-      <c r="M18" s="46" t="n"/>
+      <c r="J18" s="163" t="n"/>
+      <c r="K18" s="163" t="n"/>
+      <c r="L18" s="163" t="n"/>
+      <c r="M18" s="165" t="n"/>
       <c r="P18" s="36" t="n"/>
       <c r="Q18" s="34" t="n"/>
       <c r="R18" s="34" t="n"/>
@@ -1991,10 +2032,10 @@
       <c r="G19" s="135" t="n"/>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="77" t="n"/>
-      <c r="J19" s="72" t="n"/>
-      <c r="K19" s="72" t="n"/>
-      <c r="L19" s="72" t="n"/>
-      <c r="M19" s="46" t="n"/>
+      <c r="J19" s="163" t="n"/>
+      <c r="K19" s="163" t="n"/>
+      <c r="L19" s="163" t="n"/>
+      <c r="M19" s="165" t="n"/>
       <c r="P19" s="36" t="n"/>
       <c r="Q19" s="34" t="n"/>
       <c r="R19" s="34" t="n"/>
@@ -2014,10 +2055,10 @@
       <c r="G20" s="135" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="77" t="n"/>
-      <c r="J20" s="72" t="n"/>
-      <c r="K20" s="72" t="n"/>
-      <c r="L20" s="72" t="n"/>
-      <c r="M20" s="46" t="n"/>
+      <c r="J20" s="163" t="n"/>
+      <c r="K20" s="163" t="n"/>
+      <c r="L20" s="163" t="n"/>
+      <c r="M20" s="165" t="n"/>
       <c r="P20" s="36" t="n"/>
       <c r="Q20" s="34" t="n"/>
       <c r="R20" s="34" t="n"/>
@@ -2039,10 +2080,10 @@
       <c r="G21" s="135" t="n"/>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="77" t="n"/>
-      <c r="J21" s="72" t="n"/>
-      <c r="K21" s="72" t="n"/>
-      <c r="L21" s="72" t="n"/>
-      <c r="M21" s="46" t="n"/>
+      <c r="J21" s="163" t="n"/>
+      <c r="K21" s="163" t="n"/>
+      <c r="L21" s="163" t="n"/>
+      <c r="M21" s="165" t="n"/>
       <c r="P21" s="36" t="n"/>
       <c r="Q21" s="34" t="n"/>
       <c r="R21" s="34" t="n"/>
@@ -2067,10 +2108,10 @@
       <c r="G22" s="135" t="n"/>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="77" t="n"/>
-      <c r="J22" s="77" t="n"/>
-      <c r="K22" s="77" t="n"/>
-      <c r="L22" s="77" t="n"/>
-      <c r="M22" s="46" t="n"/>
+      <c r="J22" s="166" t="n"/>
+      <c r="K22" s="166" t="n"/>
+      <c r="L22" s="166" t="n"/>
+      <c r="M22" s="165" t="n"/>
       <c r="P22" s="37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2088,10 +2129,10 @@
       <c r="G23" s="135" t="n"/>
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="77" t="n"/>
-      <c r="J23" s="77" t="n"/>
-      <c r="K23" s="77" t="n"/>
-      <c r="L23" s="77" t="n"/>
-      <c r="M23" s="77" t="n"/>
+      <c r="J23" s="166" t="n"/>
+      <c r="K23" s="166" t="n"/>
+      <c r="L23" s="166" t="n"/>
+      <c r="M23" s="166" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" thickBot="1">
       <c r="B24" s="100" t="n"/>
@@ -2102,10 +2143,10 @@
       <c r="G24" s="152" t="n"/>
       <c r="H24" s="152" t="n"/>
       <c r="I24" s="29" t="n"/>
-      <c r="J24" s="30" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="32" t="n"/>
-      <c r="M24" s="32" t="n"/>
+      <c r="J24" s="167" t="n"/>
+      <c r="K24" s="168" t="n"/>
+      <c r="L24" s="169" t="n"/>
+      <c r="M24" s="169" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" thickBot="1">
       <c r="B25" s="153" t="n"/>
@@ -2116,10 +2157,10 @@
       <c r="G25" s="146" t="n"/>
       <c r="H25" s="146" t="n"/>
       <c r="I25" s="146" t="n"/>
-      <c r="J25" s="146" t="n"/>
-      <c r="K25" s="146" t="n"/>
-      <c r="L25" s="146" t="n"/>
-      <c r="M25" s="147" t="n"/>
+      <c r="J25" s="170" t="n"/>
+      <c r="K25" s="170" t="n"/>
+      <c r="L25" s="170" t="n"/>
+      <c r="M25" s="171" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" thickBot="1">
       <c r="B26" s="106" t="inlineStr">
@@ -2134,18 +2175,18 @@
       <c r="G26" s="146" t="n"/>
       <c r="H26" s="146" t="n"/>
       <c r="I26" s="18" t="n"/>
-      <c r="J26" s="19" t="n"/>
-      <c r="K26" s="1" t="n"/>
-      <c r="L26" s="20" t="n"/>
-      <c r="M26" s="21" t="n"/>
+      <c r="J26" s="172" t="n"/>
+      <c r="K26" s="173" t="n"/>
+      <c r="L26" s="174" t="n"/>
+      <c r="M26" s="173" t="n"/>
       <c r="O26" s="33" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
       <c r="I27" s="18" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="1" t="n"/>
-      <c r="L27" s="20" t="n"/>
-      <c r="M27" s="21" t="n"/>
+      <c r="J27" s="172" t="n"/>
+      <c r="K27" s="173" t="n"/>
+      <c r="L27" s="174" t="n"/>
+      <c r="M27" s="173" t="n"/>
       <c r="O27" s="33" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" thickBot="1">
@@ -2161,10 +2202,10 @@
       <c r="G28" s="146" t="n"/>
       <c r="H28" s="146" t="n"/>
       <c r="I28" s="18" t="n"/>
-      <c r="J28" s="21" t="n"/>
-      <c r="K28" s="1" t="n"/>
-      <c r="L28" s="20" t="n"/>
-      <c r="M28" s="21" t="n"/>
+      <c r="J28" s="173" t="n"/>
+      <c r="K28" s="173" t="n"/>
+      <c r="L28" s="174" t="n"/>
+      <c r="M28" s="173" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
       <c r="B29" s="154" t="inlineStr">
